--- a/cache/Bank_vaset.xlsx
+++ b/cache/Bank_vaset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\temp\pichNew\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F02F809-EBBE-4C8D-B295-598A68235347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B318F5-21E3-4ACC-A31B-6ED452801A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="1860" windowWidth="21600" windowHeight="11385" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="61">
   <si>
     <t>حساب بانكي كد تفصيل</t>
   </si>
@@ -213,13 +211,19 @@
   </si>
   <si>
     <t>ملي سه راه نظر 0366524661002</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>پارسیان فلکه فیض اقا مجید 200330103094655601</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,17 +613,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBF8904-44C2-442E-AAA7-1BD63394DE97}">
   <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" customWidth="1"/>
-    <col min="6" max="6" width="35.5703125" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="1" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="31.625" customWidth="1"/>
+    <col min="6" max="6" width="35.625" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -672,7 +676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="17.25" customHeight="1">
       <c r="A2">
         <v>15</v>
       </c>
@@ -722,7 +726,7 @@
         <v>111111</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>16</v>
       </c>
@@ -772,7 +776,7 @@
         <v>111111</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>17</v>
       </c>
@@ -822,7 +826,7 @@
         <v>1111111</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>18</v>
       </c>
@@ -872,7 +876,7 @@
         <v>111111</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>19</v>
       </c>
@@ -922,7 +926,7 @@
         <v>1111111</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>20</v>
       </c>
@@ -972,7 +976,7 @@
         <v>11111</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>8</v>
       </c>
@@ -1022,7 +1026,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>9</v>
       </c>
@@ -1072,7 +1076,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>10</v>
       </c>
@@ -1122,7 +1126,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>12</v>
       </c>
@@ -1172,7 +1176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>31</v>
       </c>
@@ -1186,7 +1190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>32</v>
       </c>
@@ -1200,7 +1204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="14.25" customHeight="1">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1214,7 +1218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1255,7 +1259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1290,12 +1294,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1309,7 +1322,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>5</v>
       </c>
@@ -1323,7 +1336,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>6</v>
       </c>
@@ -1337,7 +1350,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>11</v>
       </c>
